--- a/outputs/aasted3_run_comparison/summary/output_raw_data/aasted3_raw_detail_tables.xlsx
+++ b/outputs/aasted3_run_comparison/summary/output_raw_data/aasted3_raw_detail_tables.xlsx
@@ -35,8 +35,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Corrected Raw Inventory'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Experimental Setup'!$A$1:$K$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Viscosity Ratio'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Aasted Detachment Summary'!$A$1:$Y$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Aasted US Change Points'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Aasted Detachment Summary'!$A$1:$AF$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Aasted US Change Points'!$A$1:$U$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Aasted Detachment Homogeneity'!$A$1:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Aasted Parameter Landmarks'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Quality Comparison'!$A$1:$N$9</definedName>
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -739,24 +739,31 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="33" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
-    <col width="29" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
-    <col width="37" customWidth="1" min="16" max="16"/>
-    <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
     <col width="30" customWidth="1" min="21" max="21"/>
     <col width="38" customWidth="1" min="22" max="22"/>
-    <col width="38" customWidth="1" min="23" max="23"/>
+    <col width="37" customWidth="1" min="23" max="23"/>
     <col width="38" customWidth="1" min="24" max="24"/>
-    <col width="38" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="23" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="38" customWidth="1" min="29" max="29"/>
+    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="38" customWidth="1" min="31" max="31"/>
+    <col width="38" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,90 +804,125 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>analysis_domain</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_window_start_s</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>analysis_window_end_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_after_onset_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>first_change_point_zone</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_s</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_zone</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_zone_start_s</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>detachment_offset_zone_end_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>demoulding_twisting_start_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>complete_detachment_before_demoulding</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>detachment_onset_to_offset_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>detachment_offset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>detachment_onset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>crystallization_onset_minus_deposition_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>reference_us_level</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>threshold_10pct_lower</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>us_level_at_decision</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>change_points_detected_total</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>change_points_until_detachment_or_last</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pattern_description</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
@@ -916,66 +958,91 @@
       <c r="G2" t="n">
         <v>1454</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="J2" t="n">
         <v>2213.480570077896</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
+        <v>1533.480596780777</v>
+      </c>
+      <c r="L2" t="n">
+        <v>79.48059678077652</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>2073.480711936951</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="Q2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" t="n">
         <v>2118</v>
       </c>
-      <c r="M2" t="n">
+      <c r="S2" t="n">
+        <v>2118</v>
+      </c>
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="U2" t="n">
         <v>619.4807119369507</v>
       </c>
-      <c r="O2" t="n">
+      <c r="V2" t="n">
         <v>1789.480711936951</v>
       </c>
-      <c r="P2" t="n">
+      <c r="W2" t="n">
         <v>1170</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
         <v>344</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Y2" t="n">
         <v>0.9854422053609572</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Z2" t="n">
         <v>0.8868979848248615</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AA2" t="n">
         <v>0.9387736268774387</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AB2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="n">
         <v>2</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 2073.5s.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -1011,66 +1078,91 @@
       <c r="G3" t="n">
         <v>1456</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1456</v>
+      </c>
+      <c r="J3" t="n">
         <v>2213.480570077896</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
+        <v>1517.48148560524</v>
+      </c>
+      <c r="L3" t="n">
+        <v>61.48148560523987</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>2071.500448465347</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="Q3" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R3" t="n">
         <v>2118</v>
       </c>
-      <c r="M3" t="n">
+      <c r="S3" t="n">
+        <v>2118</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="U3" t="n">
         <v>615.5004484653473</v>
       </c>
-      <c r="O3" t="n">
+      <c r="V3" t="n">
         <v>1787.500448465347</v>
       </c>
-      <c r="P3" t="n">
+      <c r="W3" t="n">
         <v>1172</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
         <v>342</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Y3" t="n">
         <v>0.8087176470762016</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Z3" t="n">
         <v>0.7278458823685815</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AA3" t="n">
         <v>0.82536306643459</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AB3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AC3" t="n">
         <v>3</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>3 positive upward change point(s) from detachment onset to run end. First complete offset at 2071.5s.</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -1106,66 +1198,91 @@
       <c r="G4" t="n">
         <v>1430</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1430</v>
+      </c>
+      <c r="J4" t="n">
         <v>1868.234316587448</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
+        <v>1523.292253017426</v>
+      </c>
+      <c r="L4" t="n">
+        <v>93.29225301742554</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>1755.292186975479</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="Q4" t="n">
+        <v>1629</v>
+      </c>
+      <c r="R4" t="n">
         <v>1792</v>
       </c>
-      <c r="M4" t="n">
+      <c r="S4" t="n">
+        <v>1792</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="U4" t="n">
         <v>325.2921869754791</v>
       </c>
-      <c r="O4" t="n">
+      <c r="V4" t="n">
         <v>1469.292186975479</v>
       </c>
-      <c r="P4" t="n">
+      <c r="W4" t="n">
         <v>1144</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
         <v>344</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Y4" t="n">
         <v>0.9886593692731603</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Z4" t="n">
         <v>0.8897934323458443</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AA4" t="n">
         <v>0.9108031549980742</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AB4" t="n">
         <v>2</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AC4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1755.3s.</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
@@ -1201,73 +1318,98 @@
       <c r="G5" t="n">
         <v>1430</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="J5" t="n">
         <v>1868.234316587448</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
+        <v>1643.292067527771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>213.292067527771</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>1757.292216777802</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>complete_detachment_for_channel</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>transition_2</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="Q5" t="n">
+        <v>1629</v>
+      </c>
+      <c r="R5" t="n">
         <v>1792</v>
       </c>
-      <c r="M5" t="n">
+      <c r="S5" t="n">
+        <v>1792</v>
+      </c>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="n">
+      <c r="U5" t="n">
         <v>327.2922167778015</v>
       </c>
-      <c r="O5" t="n">
+      <c r="V5" t="n">
         <v>1471.292216777802</v>
       </c>
-      <c r="P5" t="n">
+      <c r="W5" t="n">
         <v>1144</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="X5" t="n">
         <v>344</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Y5" t="n">
         <v>0.8195161085032753</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>0.7375644976529477</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AA5" t="n">
         <v>0.8063564620894778</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AB5" t="n">
         <v>2</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AC5" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2 positive upward change point(s) from detachment onset to run end. First complete offset at 1757.3s.</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>positive/upward local mean-shift change points on T7-corrected ultrasound; complete detachment if US at change point &gt;= 10%-below-pre-deposition-reference threshold</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>aa3_trials_experimental_summary.xlsx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y5"/>
+  <autoFilter ref="A1:AF5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1278,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1290,12 +1432,18 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="31" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1346,30 +1494,60 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>detachment_onset_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>change_point_after_detachment_onset_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>change_point_zone</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_domain</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_window_start_s</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>analysis_window_end_s</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>deposition_reference_window_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>reference_us_level</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>threshold_10pct_lower</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>us_level_at_change_point</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>threshold_met</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1409,21 +1587,43 @@
       <c r="I2" t="n">
         <v>0.4802671578366529</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="K2" t="n">
+        <v>79.48059678077652</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>279.0-284.0</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="Q2" t="n">
         <v>0.9854422053609572</v>
       </c>
-      <c r="L2" t="n">
+      <c r="R2" t="n">
         <v>0.8868979848248615</v>
       </c>
-      <c r="M2" t="n">
+      <c r="S2" t="n">
         <v>0.4796810008463419</v>
       </c>
-      <c r="N2" t="n">
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1461,24 +1661,46 @@
       <c r="I3" t="n">
         <v>0.3041440342845763</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="n">
+        <v>1454</v>
+      </c>
+      <c r="K3" t="n">
+        <v>619.4807119369507</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>279.0-284.0</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="Q3" t="n">
         <v>0.9854422053609572</v>
       </c>
-      <c r="L3" t="n">
+      <c r="R3" t="n">
         <v>0.8868979848248615</v>
       </c>
-      <c r="M3" t="n">
+      <c r="S3" t="n">
         <v>0.9387736268774387</v>
       </c>
-      <c r="N3" t="n">
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>first passing change point used as detachment offset</t>
         </is>
@@ -1518,21 +1740,43 @@
       <c r="I4" t="n">
         <v>0.04680189148718228</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1456</v>
+      </c>
+      <c r="K4" t="n">
+        <v>61.48148560523987</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1456</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>279.0-284.0</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="Q4" t="n">
         <v>0.8087176470762016</v>
       </c>
-      <c r="L4" t="n">
+      <c r="R4" t="n">
         <v>0.7278458823685815</v>
       </c>
-      <c r="M4" t="n">
+      <c r="S4" t="n">
         <v>0.1652990694306293</v>
       </c>
-      <c r="N4" t="n">
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1570,21 +1814,43 @@
       <c r="I5" t="n">
         <v>0.1273577698650399</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>1456</v>
+      </c>
+      <c r="K5" t="n">
+        <v>199.4805858135228</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1456</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>279.0-284.0</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="Q5" t="n">
         <v>0.8087176470762016</v>
       </c>
-      <c r="L5" t="n">
+      <c r="R5" t="n">
         <v>0.7278458823685815</v>
       </c>
-      <c r="M5" t="n">
+      <c r="S5" t="n">
         <v>0.2661319682751241</v>
       </c>
-      <c r="N5" t="n">
+      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1622,24 +1888,46 @@
       <c r="I6" t="n">
         <v>0.7221317924475885</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="n">
+        <v>1456</v>
+      </c>
+      <c r="K6" t="n">
+        <v>615.5004484653473</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1456</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2213.480570077896</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>279.0-284.0</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="Q6" t="n">
         <v>0.8087176470762016</v>
       </c>
-      <c r="L6" t="n">
+      <c r="R6" t="n">
         <v>0.7278458823685815</v>
       </c>
-      <c r="M6" t="n">
+      <c r="S6" t="n">
         <v>0.82536306643459</v>
       </c>
-      <c r="N6" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>first passing change point used as detachment offset</t>
         </is>
@@ -1679,21 +1967,43 @@
       <c r="I7" t="n">
         <v>0.3840676706556856</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>1430</v>
+      </c>
+      <c r="K7" t="n">
+        <v>93.29225301742554</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>less_periodic_cooling_2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1430</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>281.0-286.0</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="Q7" t="n">
         <v>0.9886593692731603</v>
       </c>
-      <c r="L7" t="n">
+      <c r="R7" t="n">
         <v>0.8897934323458443</v>
       </c>
-      <c r="M7" t="n">
+      <c r="S7" t="n">
         <v>0.3570234783982772</v>
       </c>
-      <c r="N7" t="n">
+      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1731,24 +2041,46 @@
       <c r="I8" t="n">
         <v>0.4616771003871616</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1430</v>
+      </c>
+      <c r="K8" t="n">
+        <v>325.2921869754791</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1430</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>281.0-286.0</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="Q8" t="n">
         <v>0.9886593692731603</v>
       </c>
-      <c r="L8" t="n">
+      <c r="R8" t="n">
         <v>0.8897934323458443</v>
       </c>
-      <c r="M8" t="n">
+      <c r="S8" t="n">
         <v>0.9108031549980742</v>
       </c>
-      <c r="N8" t="n">
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>first passing change point used as detachment offset</t>
         </is>
@@ -1788,21 +2120,43 @@
       <c r="I9" t="n">
         <v>0.1816815349636445</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="K9" t="n">
+        <v>213.292067527771</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>1430</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>281.0-286.0</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="Q9" t="n">
         <v>0.8195161085032753</v>
       </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
         <v>0.7375644976529477</v>
       </c>
-      <c r="M9" t="n">
+      <c r="S9" t="n">
         <v>0.2432728566849877</v>
       </c>
-      <c r="N9" t="n">
+      <c r="T9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1840,31 +2194,53 @@
       <c r="I10" t="n">
         <v>0.5308918908308495</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1430</v>
+      </c>
+      <c r="K10" t="n">
+        <v>327.2922167778015</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>transition_2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>detachment_onset_to_run_end</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1430</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1868.234316587448</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>281.0-286.0</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="Q10" t="n">
         <v>0.8195161085032753</v>
       </c>
-      <c r="L10" t="n">
+      <c r="R10" t="n">
         <v>0.7375644976529477</v>
       </c>
-      <c r="M10" t="n">
+      <c r="S10" t="n">
         <v>0.8063564620894778</v>
       </c>
-      <c r="N10" t="n">
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>first passing change point used as detachment offset</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/outputs/aasted3_run_comparison/summary/output_raw_data/aasted3_raw_detail_tables.xlsx
+++ b/outputs/aasted3_run_comparison/summary/output_raw_data/aasted3_raw_detail_tables.xlsx
@@ -28,7 +28,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Detected Duration'!$A$1:$D$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Delta By Zone'!$A$1:$E$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detected Product By Zone'!$A$1:$H$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Detected Product By Zone'!$A$1:$P$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Detected Product Delta'!$A$1:$E$85</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hotspot Sensor Data'!$A$1:$I$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Temperature Correction'!$A$1:$I$5</definedName>
@@ -51543,7 +51543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:P169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -51554,6 +51554,14 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="38" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -51597,6 +51605,46 @@
           <t>n_temp_points</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>deposition_s</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>mould_temperature_deposition_C</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>mould_temperature_deposition_sensor</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>mould_temperature_deposition_window_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>chocolate_temperature_deposition_C</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>chocolate_temperature_deposition_sensors</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>chocolate_temperature_deposition_window_s</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>deposition_temperature_method</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -51629,6 +51677,40 @@
       <c r="H2" t="n">
         <v>10</v>
       </c>
+      <c r="I2" t="n">
+        <v>286</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -51661,6 +51743,40 @@
       <c r="H3" t="n">
         <v>10</v>
       </c>
+      <c r="I3" t="n">
+        <v>286</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -51693,6 +51809,40 @@
       <c r="H4" t="n">
         <v>10</v>
       </c>
+      <c r="I4" t="n">
+        <v>286</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -51725,6 +51875,40 @@
       <c r="H5" t="n">
         <v>10</v>
       </c>
+      <c r="I5" t="n">
+        <v>286</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51757,6 +51941,40 @@
       <c r="H6" t="n">
         <v>10</v>
       </c>
+      <c r="I6" t="n">
+        <v>286</v>
+      </c>
+      <c r="J6" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -51789,6 +52007,40 @@
       <c r="H7" t="n">
         <v>10</v>
       </c>
+      <c r="I7" t="n">
+        <v>286</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -51821,6 +52073,40 @@
       <c r="H8" t="n">
         <v>96</v>
       </c>
+      <c r="I8" t="n">
+        <v>286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -51853,6 +52139,40 @@
       <c r="H9" t="n">
         <v>96</v>
       </c>
+      <c r="I9" t="n">
+        <v>286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -51885,6 +52205,40 @@
       <c r="H10" t="n">
         <v>96</v>
       </c>
+      <c r="I10" t="n">
+        <v>286</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -51917,6 +52271,40 @@
       <c r="H11" t="n">
         <v>96</v>
       </c>
+      <c r="I11" t="n">
+        <v>286</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -51949,6 +52337,40 @@
       <c r="H12" t="n">
         <v>96</v>
       </c>
+      <c r="I12" t="n">
+        <v>286</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -51981,6 +52403,40 @@
       <c r="H13" t="n">
         <v>96</v>
       </c>
+      <c r="I13" t="n">
+        <v>286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -52013,6 +52469,40 @@
       <c r="H14" t="n">
         <v>50</v>
       </c>
+      <c r="I14" t="n">
+        <v>286</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -52045,6 +52535,40 @@
       <c r="H15" t="n">
         <v>50</v>
       </c>
+      <c r="I15" t="n">
+        <v>286</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -52077,6 +52601,40 @@
       <c r="H16" t="n">
         <v>50</v>
       </c>
+      <c r="I16" t="n">
+        <v>286</v>
+      </c>
+      <c r="J16" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -52109,6 +52667,40 @@
       <c r="H17" t="n">
         <v>50</v>
       </c>
+      <c r="I17" t="n">
+        <v>286</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -52141,6 +52733,40 @@
       <c r="H18" t="n">
         <v>50</v>
       </c>
+      <c r="I18" t="n">
+        <v>286</v>
+      </c>
+      <c r="J18" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -52173,6 +52799,40 @@
       <c r="H19" t="n">
         <v>50</v>
       </c>
+      <c r="I19" t="n">
+        <v>286</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -52205,6 +52865,40 @@
       <c r="H20" t="n">
         <v>59</v>
       </c>
+      <c r="I20" t="n">
+        <v>286</v>
+      </c>
+      <c r="J20" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52237,6 +52931,40 @@
       <c r="H21" t="n">
         <v>59</v>
       </c>
+      <c r="I21" t="n">
+        <v>286</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52269,6 +52997,40 @@
       <c r="H22" t="n">
         <v>59</v>
       </c>
+      <c r="I22" t="n">
+        <v>286</v>
+      </c>
+      <c r="J22" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -52301,6 +53063,40 @@
       <c r="H23" t="n">
         <v>59</v>
       </c>
+      <c r="I23" t="n">
+        <v>286</v>
+      </c>
+      <c r="J23" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -52333,6 +53129,40 @@
       <c r="H24" t="n">
         <v>59</v>
       </c>
+      <c r="I24" t="n">
+        <v>286</v>
+      </c>
+      <c r="J24" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -52365,6 +53195,40 @@
       <c r="H25" t="n">
         <v>59</v>
       </c>
+      <c r="I25" t="n">
+        <v>286</v>
+      </c>
+      <c r="J25" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -52397,6 +53261,40 @@
       <c r="H26" t="n">
         <v>42</v>
       </c>
+      <c r="I26" t="n">
+        <v>286</v>
+      </c>
+      <c r="J26" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -52429,6 +53327,40 @@
       <c r="H27" t="n">
         <v>42</v>
       </c>
+      <c r="I27" t="n">
+        <v>286</v>
+      </c>
+      <c r="J27" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -52461,6 +53393,40 @@
       <c r="H28" t="n">
         <v>42</v>
       </c>
+      <c r="I28" t="n">
+        <v>286</v>
+      </c>
+      <c r="J28" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -52493,6 +53459,40 @@
       <c r="H29" t="n">
         <v>42</v>
       </c>
+      <c r="I29" t="n">
+        <v>286</v>
+      </c>
+      <c r="J29" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -52525,6 +53525,40 @@
       <c r="H30" t="n">
         <v>42</v>
       </c>
+      <c r="I30" t="n">
+        <v>286</v>
+      </c>
+      <c r="J30" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -52557,6 +53591,40 @@
       <c r="H31" t="n">
         <v>42</v>
       </c>
+      <c r="I31" t="n">
+        <v>286</v>
+      </c>
+      <c r="J31" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -52589,6 +53657,40 @@
       <c r="H32" t="n">
         <v>49</v>
       </c>
+      <c r="I32" t="n">
+        <v>286</v>
+      </c>
+      <c r="J32" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -52621,6 +53723,40 @@
       <c r="H33" t="n">
         <v>49</v>
       </c>
+      <c r="I33" t="n">
+        <v>286</v>
+      </c>
+      <c r="J33" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -52653,6 +53789,40 @@
       <c r="H34" t="n">
         <v>49</v>
       </c>
+      <c r="I34" t="n">
+        <v>286</v>
+      </c>
+      <c r="J34" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -52685,6 +53855,40 @@
       <c r="H35" t="n">
         <v>49</v>
       </c>
+      <c r="I35" t="n">
+        <v>286</v>
+      </c>
+      <c r="J35" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -52717,6 +53921,40 @@
       <c r="H36" t="n">
         <v>49</v>
       </c>
+      <c r="I36" t="n">
+        <v>286</v>
+      </c>
+      <c r="J36" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -52749,6 +53987,40 @@
       <c r="H37" t="n">
         <v>49</v>
       </c>
+      <c r="I37" t="n">
+        <v>286</v>
+      </c>
+      <c r="J37" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -52781,6 +54053,40 @@
       <c r="H38" t="n">
         <v>69</v>
       </c>
+      <c r="I38" t="n">
+        <v>286</v>
+      </c>
+      <c r="J38" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -52813,6 +54119,40 @@
       <c r="H39" t="n">
         <v>69</v>
       </c>
+      <c r="I39" t="n">
+        <v>286</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -52845,6 +54185,40 @@
       <c r="H40" t="n">
         <v>69</v>
       </c>
+      <c r="I40" t="n">
+        <v>286</v>
+      </c>
+      <c r="J40" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -52877,6 +54251,40 @@
       <c r="H41" t="n">
         <v>69</v>
       </c>
+      <c r="I41" t="n">
+        <v>286</v>
+      </c>
+      <c r="J41" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -52909,6 +54317,40 @@
       <c r="H42" t="n">
         <v>69</v>
       </c>
+      <c r="I42" t="n">
+        <v>286</v>
+      </c>
+      <c r="J42" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -52941,6 +54383,40 @@
       <c r="H43" t="n">
         <v>69</v>
       </c>
+      <c r="I43" t="n">
+        <v>286</v>
+      </c>
+      <c r="J43" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -52973,6 +54449,40 @@
       <c r="H44" t="n">
         <v>69</v>
       </c>
+      <c r="I44" t="n">
+        <v>286</v>
+      </c>
+      <c r="J44" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -53005,6 +54515,40 @@
       <c r="H45" t="n">
         <v>69</v>
       </c>
+      <c r="I45" t="n">
+        <v>286</v>
+      </c>
+      <c r="J45" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -53037,6 +54581,40 @@
       <c r="H46" t="n">
         <v>69</v>
       </c>
+      <c r="I46" t="n">
+        <v>286</v>
+      </c>
+      <c r="J46" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -53069,6 +54647,40 @@
       <c r="H47" t="n">
         <v>69</v>
       </c>
+      <c r="I47" t="n">
+        <v>286</v>
+      </c>
+      <c r="J47" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -53101,6 +54713,40 @@
       <c r="H48" t="n">
         <v>69</v>
       </c>
+      <c r="I48" t="n">
+        <v>286</v>
+      </c>
+      <c r="J48" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -53133,6 +54779,40 @@
       <c r="H49" t="n">
         <v>69</v>
       </c>
+      <c r="I49" t="n">
+        <v>286</v>
+      </c>
+      <c r="J49" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -53165,6 +54845,40 @@
       <c r="H50" t="n">
         <v>69</v>
       </c>
+      <c r="I50" t="n">
+        <v>286</v>
+      </c>
+      <c r="J50" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -53197,6 +54911,40 @@
       <c r="H51" t="n">
         <v>69</v>
       </c>
+      <c r="I51" t="n">
+        <v>286</v>
+      </c>
+      <c r="J51" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -53229,6 +54977,40 @@
       <c r="H52" t="n">
         <v>69</v>
       </c>
+      <c r="I52" t="n">
+        <v>286</v>
+      </c>
+      <c r="J52" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -53261,6 +55043,40 @@
       <c r="H53" t="n">
         <v>69</v>
       </c>
+      <c r="I53" t="n">
+        <v>286</v>
+      </c>
+      <c r="J53" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -53293,6 +55109,40 @@
       <c r="H54" t="n">
         <v>69</v>
       </c>
+      <c r="I54" t="n">
+        <v>286</v>
+      </c>
+      <c r="J54" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -53325,6 +55175,40 @@
       <c r="H55" t="n">
         <v>69</v>
       </c>
+      <c r="I55" t="n">
+        <v>286</v>
+      </c>
+      <c r="J55" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -53357,6 +55241,40 @@
       <c r="H56" t="n">
         <v>301</v>
       </c>
+      <c r="I56" t="n">
+        <v>286</v>
+      </c>
+      <c r="J56" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -53389,6 +55307,40 @@
       <c r="H57" t="n">
         <v>301</v>
       </c>
+      <c r="I57" t="n">
+        <v>286</v>
+      </c>
+      <c r="J57" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -53421,6 +55373,40 @@
       <c r="H58" t="n">
         <v>301</v>
       </c>
+      <c r="I58" t="n">
+        <v>286</v>
+      </c>
+      <c r="J58" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -53453,6 +55439,40 @@
       <c r="H59" t="n">
         <v>301</v>
       </c>
+      <c r="I59" t="n">
+        <v>286</v>
+      </c>
+      <c r="J59" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -53485,6 +55505,40 @@
       <c r="H60" t="n">
         <v>301</v>
       </c>
+      <c r="I60" t="n">
+        <v>286</v>
+      </c>
+      <c r="J60" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -53517,6 +55571,40 @@
       <c r="H61" t="n">
         <v>301</v>
       </c>
+      <c r="I61" t="n">
+        <v>286</v>
+      </c>
+      <c r="J61" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -53549,6 +55637,40 @@
       <c r="H62" t="n">
         <v>82</v>
       </c>
+      <c r="I62" t="n">
+        <v>286</v>
+      </c>
+      <c r="J62" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -53581,6 +55703,40 @@
       <c r="H63" t="n">
         <v>82</v>
       </c>
+      <c r="I63" t="n">
+        <v>286</v>
+      </c>
+      <c r="J63" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -53613,6 +55769,40 @@
       <c r="H64" t="n">
         <v>82</v>
       </c>
+      <c r="I64" t="n">
+        <v>286</v>
+      </c>
+      <c r="J64" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -53645,6 +55835,40 @@
       <c r="H65" t="n">
         <v>82</v>
       </c>
+      <c r="I65" t="n">
+        <v>286</v>
+      </c>
+      <c r="J65" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -53677,6 +55901,40 @@
       <c r="H66" t="n">
         <v>82</v>
       </c>
+      <c r="I66" t="n">
+        <v>286</v>
+      </c>
+      <c r="J66" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -53709,6 +55967,40 @@
       <c r="H67" t="n">
         <v>82</v>
       </c>
+      <c r="I67" t="n">
+        <v>286</v>
+      </c>
+      <c r="J67" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -53741,6 +56033,40 @@
       <c r="H68" t="n">
         <v>3</v>
       </c>
+      <c r="I68" t="n">
+        <v>286</v>
+      </c>
+      <c r="J68" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -53773,6 +56099,40 @@
       <c r="H69" t="n">
         <v>3</v>
       </c>
+      <c r="I69" t="n">
+        <v>286</v>
+      </c>
+      <c r="J69" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -53805,6 +56165,40 @@
       <c r="H70" t="n">
         <v>3</v>
       </c>
+      <c r="I70" t="n">
+        <v>286</v>
+      </c>
+      <c r="J70" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -53837,6 +56231,40 @@
       <c r="H71" t="n">
         <v>3</v>
       </c>
+      <c r="I71" t="n">
+        <v>286</v>
+      </c>
+      <c r="J71" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -53869,6 +56297,40 @@
       <c r="H72" t="n">
         <v>3</v>
       </c>
+      <c r="I72" t="n">
+        <v>286</v>
+      </c>
+      <c r="J72" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -53901,6 +56363,40 @@
       <c r="H73" t="n">
         <v>3</v>
       </c>
+      <c r="I73" t="n">
+        <v>286</v>
+      </c>
+      <c r="J73" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -53933,6 +56429,40 @@
       <c r="H74" t="n">
         <v>29</v>
       </c>
+      <c r="I74" t="n">
+        <v>286</v>
+      </c>
+      <c r="J74" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -53965,6 +56495,40 @@
       <c r="H75" t="n">
         <v>29</v>
       </c>
+      <c r="I75" t="n">
+        <v>286</v>
+      </c>
+      <c r="J75" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -53997,6 +56561,40 @@
       <c r="H76" t="n">
         <v>29</v>
       </c>
+      <c r="I76" t="n">
+        <v>286</v>
+      </c>
+      <c r="J76" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -54029,6 +56627,40 @@
       <c r="H77" t="n">
         <v>29</v>
       </c>
+      <c r="I77" t="n">
+        <v>286</v>
+      </c>
+      <c r="J77" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -54061,6 +56693,40 @@
       <c r="H78" t="n">
         <v>29</v>
       </c>
+      <c r="I78" t="n">
+        <v>286</v>
+      </c>
+      <c r="J78" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -54093,6 +56759,40 @@
       <c r="H79" t="n">
         <v>29</v>
       </c>
+      <c r="I79" t="n">
+        <v>286</v>
+      </c>
+      <c r="J79" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -54125,6 +56825,40 @@
       <c r="H80" t="n">
         <v>4</v>
       </c>
+      <c r="I80" t="n">
+        <v>286</v>
+      </c>
+      <c r="J80" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -54157,6 +56891,40 @@
       <c r="H81" t="n">
         <v>4</v>
       </c>
+      <c r="I81" t="n">
+        <v>286</v>
+      </c>
+      <c r="J81" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -54189,6 +56957,40 @@
       <c r="H82" t="n">
         <v>4</v>
       </c>
+      <c r="I82" t="n">
+        <v>286</v>
+      </c>
+      <c r="J82" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -54221,6 +57023,40 @@
       <c r="H83" t="n">
         <v>4</v>
       </c>
+      <c r="I83" t="n">
+        <v>286</v>
+      </c>
+      <c r="J83" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -54253,6 +57089,40 @@
       <c r="H84" t="n">
         <v>4</v>
       </c>
+      <c r="I84" t="n">
+        <v>286</v>
+      </c>
+      <c r="J84" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -54285,6 +57155,40 @@
       <c r="H85" t="n">
         <v>4</v>
       </c>
+      <c r="I85" t="n">
+        <v>286</v>
+      </c>
+      <c r="J85" t="n">
+        <v>27.79296875</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>281.0-286.0</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>28.006103515625</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>306.0-311.0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -54317,6 +57221,40 @@
       <c r="H86" t="n">
         <v>13</v>
       </c>
+      <c r="I86" t="n">
+        <v>284</v>
+      </c>
+      <c r="J86" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -54349,6 +57287,40 @@
       <c r="H87" t="n">
         <v>13</v>
       </c>
+      <c r="I87" t="n">
+        <v>284</v>
+      </c>
+      <c r="J87" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -54381,6 +57353,40 @@
       <c r="H88" t="n">
         <v>13</v>
       </c>
+      <c r="I88" t="n">
+        <v>284</v>
+      </c>
+      <c r="J88" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -54413,6 +57419,40 @@
       <c r="H89" t="n">
         <v>13</v>
       </c>
+      <c r="I89" t="n">
+        <v>284</v>
+      </c>
+      <c r="J89" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -54445,6 +57485,40 @@
       <c r="H90" t="n">
         <v>13</v>
       </c>
+      <c r="I90" t="n">
+        <v>284</v>
+      </c>
+      <c r="J90" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -54477,6 +57551,40 @@
       <c r="H91" t="n">
         <v>13</v>
       </c>
+      <c r="I91" t="n">
+        <v>284</v>
+      </c>
+      <c r="J91" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -54509,6 +57617,40 @@
       <c r="H92" t="n">
         <v>94</v>
       </c>
+      <c r="I92" t="n">
+        <v>284</v>
+      </c>
+      <c r="J92" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -54541,6 +57683,40 @@
       <c r="H93" t="n">
         <v>94</v>
       </c>
+      <c r="I93" t="n">
+        <v>284</v>
+      </c>
+      <c r="J93" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -54573,6 +57749,40 @@
       <c r="H94" t="n">
         <v>94</v>
       </c>
+      <c r="I94" t="n">
+        <v>284</v>
+      </c>
+      <c r="J94" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -54605,6 +57815,40 @@
       <c r="H95" t="n">
         <v>94</v>
       </c>
+      <c r="I95" t="n">
+        <v>284</v>
+      </c>
+      <c r="J95" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -54637,6 +57881,40 @@
       <c r="H96" t="n">
         <v>94</v>
       </c>
+      <c r="I96" t="n">
+        <v>284</v>
+      </c>
+      <c r="J96" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -54669,6 +57947,40 @@
       <c r="H97" t="n">
         <v>94</v>
       </c>
+      <c r="I97" t="n">
+        <v>284</v>
+      </c>
+      <c r="J97" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -54701,6 +58013,40 @@
       <c r="H98" t="n">
         <v>50</v>
       </c>
+      <c r="I98" t="n">
+        <v>284</v>
+      </c>
+      <c r="J98" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -54733,6 +58079,40 @@
       <c r="H99" t="n">
         <v>50</v>
       </c>
+      <c r="I99" t="n">
+        <v>284</v>
+      </c>
+      <c r="J99" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -54765,6 +58145,40 @@
       <c r="H100" t="n">
         <v>50</v>
       </c>
+      <c r="I100" t="n">
+        <v>284</v>
+      </c>
+      <c r="J100" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -54797,6 +58211,40 @@
       <c r="H101" t="n">
         <v>50</v>
       </c>
+      <c r="I101" t="n">
+        <v>284</v>
+      </c>
+      <c r="J101" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -54829,6 +58277,40 @@
       <c r="H102" t="n">
         <v>50</v>
       </c>
+      <c r="I102" t="n">
+        <v>284</v>
+      </c>
+      <c r="J102" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -54861,6 +58343,40 @@
       <c r="H103" t="n">
         <v>50</v>
       </c>
+      <c r="I103" t="n">
+        <v>284</v>
+      </c>
+      <c r="J103" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -54893,6 +58409,40 @@
       <c r="H104" t="n">
         <v>30</v>
       </c>
+      <c r="I104" t="n">
+        <v>284</v>
+      </c>
+      <c r="J104" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -54925,6 +58475,40 @@
       <c r="H105" t="n">
         <v>30</v>
       </c>
+      <c r="I105" t="n">
+        <v>284</v>
+      </c>
+      <c r="J105" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -54957,6 +58541,40 @@
       <c r="H106" t="n">
         <v>30</v>
       </c>
+      <c r="I106" t="n">
+        <v>284</v>
+      </c>
+      <c r="J106" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -54989,6 +58607,40 @@
       <c r="H107" t="n">
         <v>30</v>
       </c>
+      <c r="I107" t="n">
+        <v>284</v>
+      </c>
+      <c r="J107" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -55021,6 +58673,40 @@
       <c r="H108" t="n">
         <v>30</v>
       </c>
+      <c r="I108" t="n">
+        <v>284</v>
+      </c>
+      <c r="J108" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -55053,6 +58739,40 @@
       <c r="H109" t="n">
         <v>30</v>
       </c>
+      <c r="I109" t="n">
+        <v>284</v>
+      </c>
+      <c r="J109" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -55085,6 +58805,40 @@
       <c r="H110" t="n">
         <v>72</v>
       </c>
+      <c r="I110" t="n">
+        <v>284</v>
+      </c>
+      <c r="J110" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -55117,6 +58871,40 @@
       <c r="H111" t="n">
         <v>72</v>
       </c>
+      <c r="I111" t="n">
+        <v>284</v>
+      </c>
+      <c r="J111" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -55149,6 +58937,40 @@
       <c r="H112" t="n">
         <v>72</v>
       </c>
+      <c r="I112" t="n">
+        <v>284</v>
+      </c>
+      <c r="J112" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -55181,6 +59003,40 @@
       <c r="H113" t="n">
         <v>72</v>
       </c>
+      <c r="I113" t="n">
+        <v>284</v>
+      </c>
+      <c r="J113" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M113" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -55213,6 +59069,40 @@
       <c r="H114" t="n">
         <v>72</v>
       </c>
+      <c r="I114" t="n">
+        <v>284</v>
+      </c>
+      <c r="J114" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M114" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -55245,6 +59135,40 @@
       <c r="H115" t="n">
         <v>72</v>
       </c>
+      <c r="I115" t="n">
+        <v>284</v>
+      </c>
+      <c r="J115" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M115" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -55277,6 +59201,40 @@
       <c r="H116" t="n">
         <v>49</v>
       </c>
+      <c r="I116" t="n">
+        <v>284</v>
+      </c>
+      <c r="J116" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M116" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -55309,6 +59267,40 @@
       <c r="H117" t="n">
         <v>49</v>
       </c>
+      <c r="I117" t="n">
+        <v>284</v>
+      </c>
+      <c r="J117" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M117" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -55341,6 +59333,40 @@
       <c r="H118" t="n">
         <v>49</v>
       </c>
+      <c r="I118" t="n">
+        <v>284</v>
+      </c>
+      <c r="J118" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M118" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -55373,6 +59399,40 @@
       <c r="H119" t="n">
         <v>49</v>
       </c>
+      <c r="I119" t="n">
+        <v>284</v>
+      </c>
+      <c r="J119" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M119" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -55405,6 +59465,40 @@
       <c r="H120" t="n">
         <v>49</v>
       </c>
+      <c r="I120" t="n">
+        <v>284</v>
+      </c>
+      <c r="J120" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -55437,6 +59531,40 @@
       <c r="H121" t="n">
         <v>49</v>
       </c>
+      <c r="I121" t="n">
+        <v>284</v>
+      </c>
+      <c r="J121" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -55469,6 +59597,40 @@
       <c r="H122" t="n">
         <v>88</v>
       </c>
+      <c r="I122" t="n">
+        <v>284</v>
+      </c>
+      <c r="J122" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -55501,6 +59663,40 @@
       <c r="H123" t="n">
         <v>88</v>
       </c>
+      <c r="I123" t="n">
+        <v>284</v>
+      </c>
+      <c r="J123" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M123" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -55533,6 +59729,40 @@
       <c r="H124" t="n">
         <v>88</v>
       </c>
+      <c r="I124" t="n">
+        <v>284</v>
+      </c>
+      <c r="J124" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M124" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -55565,6 +59795,40 @@
       <c r="H125" t="n">
         <v>88</v>
       </c>
+      <c r="I125" t="n">
+        <v>284</v>
+      </c>
+      <c r="J125" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M125" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -55597,6 +59861,40 @@
       <c r="H126" t="n">
         <v>88</v>
       </c>
+      <c r="I126" t="n">
+        <v>284</v>
+      </c>
+      <c r="J126" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M126" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -55629,6 +59927,40 @@
       <c r="H127" t="n">
         <v>88</v>
       </c>
+      <c r="I127" t="n">
+        <v>284</v>
+      </c>
+      <c r="J127" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M127" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -55661,6 +59993,40 @@
       <c r="H128" t="n">
         <v>54</v>
       </c>
+      <c r="I128" t="n">
+        <v>284</v>
+      </c>
+      <c r="J128" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M128" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -55693,6 +60059,40 @@
       <c r="H129" t="n">
         <v>54</v>
       </c>
+      <c r="I129" t="n">
+        <v>284</v>
+      </c>
+      <c r="J129" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M129" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -55725,6 +60125,40 @@
       <c r="H130" t="n">
         <v>54</v>
       </c>
+      <c r="I130" t="n">
+        <v>284</v>
+      </c>
+      <c r="J130" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M130" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -55757,6 +60191,40 @@
       <c r="H131" t="n">
         <v>54</v>
       </c>
+      <c r="I131" t="n">
+        <v>284</v>
+      </c>
+      <c r="J131" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M131" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -55789,6 +60257,40 @@
       <c r="H132" t="n">
         <v>54</v>
       </c>
+      <c r="I132" t="n">
+        <v>284</v>
+      </c>
+      <c r="J132" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M132" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -55821,6 +60323,40 @@
       <c r="H133" t="n">
         <v>54</v>
       </c>
+      <c r="I133" t="n">
+        <v>284</v>
+      </c>
+      <c r="J133" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M133" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -55853,6 +60389,40 @@
       <c r="H134" t="n">
         <v>62</v>
       </c>
+      <c r="I134" t="n">
+        <v>284</v>
+      </c>
+      <c r="J134" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M134" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -55885,6 +60455,40 @@
       <c r="H135" t="n">
         <v>62</v>
       </c>
+      <c r="I135" t="n">
+        <v>284</v>
+      </c>
+      <c r="J135" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M135" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -55917,6 +60521,40 @@
       <c r="H136" t="n">
         <v>62</v>
       </c>
+      <c r="I136" t="n">
+        <v>284</v>
+      </c>
+      <c r="J136" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M136" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -55949,6 +60587,40 @@
       <c r="H137" t="n">
         <v>62</v>
       </c>
+      <c r="I137" t="n">
+        <v>284</v>
+      </c>
+      <c r="J137" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M137" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -55981,6 +60653,40 @@
       <c r="H138" t="n">
         <v>62</v>
       </c>
+      <c r="I138" t="n">
+        <v>284</v>
+      </c>
+      <c r="J138" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M138" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -56013,6 +60719,40 @@
       <c r="H139" t="n">
         <v>62</v>
       </c>
+      <c r="I139" t="n">
+        <v>284</v>
+      </c>
+      <c r="J139" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M139" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -56045,6 +60785,40 @@
       <c r="H140" t="n">
         <v>476</v>
       </c>
+      <c r="I140" t="n">
+        <v>284</v>
+      </c>
+      <c r="J140" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -56077,6 +60851,40 @@
       <c r="H141" t="n">
         <v>476</v>
       </c>
+      <c r="I141" t="n">
+        <v>284</v>
+      </c>
+      <c r="J141" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -56109,6 +60917,40 @@
       <c r="H142" t="n">
         <v>476</v>
       </c>
+      <c r="I142" t="n">
+        <v>284</v>
+      </c>
+      <c r="J142" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -56141,6 +60983,40 @@
       <c r="H143" t="n">
         <v>476</v>
       </c>
+      <c r="I143" t="n">
+        <v>284</v>
+      </c>
+      <c r="J143" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M143" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -56173,6 +61049,40 @@
       <c r="H144" t="n">
         <v>476</v>
       </c>
+      <c r="I144" t="n">
+        <v>284</v>
+      </c>
+      <c r="J144" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M144" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -56205,6 +61115,40 @@
       <c r="H145" t="n">
         <v>476</v>
       </c>
+      <c r="I145" t="n">
+        <v>284</v>
+      </c>
+      <c r="J145" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M145" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -56237,6 +61181,40 @@
       <c r="H146" t="n">
         <v>71</v>
       </c>
+      <c r="I146" t="n">
+        <v>284</v>
+      </c>
+      <c r="J146" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M146" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -56269,6 +61247,40 @@
       <c r="H147" t="n">
         <v>71</v>
       </c>
+      <c r="I147" t="n">
+        <v>284</v>
+      </c>
+      <c r="J147" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M147" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -56301,6 +61313,40 @@
       <c r="H148" t="n">
         <v>71</v>
       </c>
+      <c r="I148" t="n">
+        <v>284</v>
+      </c>
+      <c r="J148" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M148" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -56333,6 +61379,40 @@
       <c r="H149" t="n">
         <v>71</v>
       </c>
+      <c r="I149" t="n">
+        <v>284</v>
+      </c>
+      <c r="J149" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M149" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -56365,6 +61445,40 @@
       <c r="H150" t="n">
         <v>71</v>
       </c>
+      <c r="I150" t="n">
+        <v>284</v>
+      </c>
+      <c r="J150" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M150" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -56397,6 +61511,40 @@
       <c r="H151" t="n">
         <v>71</v>
       </c>
+      <c r="I151" t="n">
+        <v>284</v>
+      </c>
+      <c r="J151" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M151" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -56429,6 +61577,40 @@
       <c r="H152" t="n">
         <v>4</v>
       </c>
+      <c r="I152" t="n">
+        <v>284</v>
+      </c>
+      <c r="J152" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M152" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -56461,6 +61643,40 @@
       <c r="H153" t="n">
         <v>4</v>
       </c>
+      <c r="I153" t="n">
+        <v>284</v>
+      </c>
+      <c r="J153" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M153" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -56493,6 +61709,40 @@
       <c r="H154" t="n">
         <v>4</v>
       </c>
+      <c r="I154" t="n">
+        <v>284</v>
+      </c>
+      <c r="J154" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M154" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -56525,6 +61775,40 @@
       <c r="H155" t="n">
         <v>4</v>
       </c>
+      <c r="I155" t="n">
+        <v>284</v>
+      </c>
+      <c r="J155" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M155" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -56557,6 +61841,40 @@
       <c r="H156" t="n">
         <v>4</v>
       </c>
+      <c r="I156" t="n">
+        <v>284</v>
+      </c>
+      <c r="J156" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M156" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -56589,6 +61907,40 @@
       <c r="H157" t="n">
         <v>4</v>
       </c>
+      <c r="I157" t="n">
+        <v>284</v>
+      </c>
+      <c r="J157" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M157" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -56621,6 +61973,40 @@
       <c r="H158" t="n">
         <v>30</v>
       </c>
+      <c r="I158" t="n">
+        <v>284</v>
+      </c>
+      <c r="J158" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M158" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -56653,6 +62039,40 @@
       <c r="H159" t="n">
         <v>30</v>
       </c>
+      <c r="I159" t="n">
+        <v>284</v>
+      </c>
+      <c r="J159" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M159" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -56685,6 +62105,40 @@
       <c r="H160" t="n">
         <v>30</v>
       </c>
+      <c r="I160" t="n">
+        <v>284</v>
+      </c>
+      <c r="J160" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M160" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -56717,6 +62171,40 @@
       <c r="H161" t="n">
         <v>30</v>
       </c>
+      <c r="I161" t="n">
+        <v>284</v>
+      </c>
+      <c r="J161" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M161" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -56749,6 +62237,40 @@
       <c r="H162" t="n">
         <v>30</v>
       </c>
+      <c r="I162" t="n">
+        <v>284</v>
+      </c>
+      <c r="J162" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M162" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -56781,6 +62303,40 @@
       <c r="H163" t="n">
         <v>30</v>
       </c>
+      <c r="I163" t="n">
+        <v>284</v>
+      </c>
+      <c r="J163" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M163" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -56813,6 +62369,40 @@
       <c r="H164" t="n">
         <v>12</v>
       </c>
+      <c r="I164" t="n">
+        <v>284</v>
+      </c>
+      <c r="J164" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M164" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -56845,6 +62435,40 @@
       <c r="H165" t="n">
         <v>12</v>
       </c>
+      <c r="I165" t="n">
+        <v>284</v>
+      </c>
+      <c r="J165" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M165" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -56877,6 +62501,40 @@
       <c r="H166" t="n">
         <v>12</v>
       </c>
+      <c r="I166" t="n">
+        <v>284</v>
+      </c>
+      <c r="J166" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M166" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -56909,6 +62567,40 @@
       <c r="H167" t="n">
         <v>12</v>
       </c>
+      <c r="I167" t="n">
+        <v>284</v>
+      </c>
+      <c r="J167" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M167" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -56941,6 +62633,40 @@
       <c r="H168" t="n">
         <v>12</v>
       </c>
+      <c r="I168" t="n">
+        <v>284</v>
+      </c>
+      <c r="J168" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -56973,9 +62699,43 @@
       <c r="H169" t="n">
         <v>12</v>
       </c>
+      <c r="I169" t="n">
+        <v>284</v>
+      </c>
+      <c r="J169" t="n">
+        <v>26.65234375</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>279.0-284.0</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>27.111572265625</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>T2, T3, T4, T5</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>304.0-309.0</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>mould = median T7 from 5 s before deposition to deposition; chocolate = median row-wise mean of product sensors excluding T7 from 20-25 s after deposition</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H169"/>
+  <autoFilter ref="A1:P169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
